--- a/planos_empresas/plano_empresa_20144.xlsx
+++ b/planos_empresas/plano_empresa_20144.xlsx
@@ -413,9 +413,85 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>010501 - Licenciamento ou cessão de direito de uso de programas de computação.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>100201 - 10.02 - Agenciamento, corretagem ou intermediação de títulos em geral, valores mobiliários, contratos quaisquer.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>170102 - Análise, exame, pesquisa, coleta, compilação e fornecimento de dados e informações de qualquer natureza, inclusive cadastro e similares.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>170601 - Propaganda e publicidade, inclusive promoção de vendas, planejamento de campanhas ou sistemas de publicidade, elaboração de desenhos, textos e demais materiais publicitários.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>172501 - Inserção de textos, desenhos e outros materiais de propaganda e publicidade, em qualquer meio (excet</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/planos_empresas/plano_empresa_20144.xlsx
+++ b/planos_empresas/plano_empresa_20144.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,6 +491,66 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>140601 - Instalação e montagem de aparelhos, máquinas e equipamentos, inclusive montagem industrial, prestados ao usuário final, exclusivamente com material por ele fornecido.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>170101 - Assessoria ou consultoria de qualquer natureza, não contida em outros itens desta lista.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>171201 - Administração em geral, inclusive de bens e negócios de terceiros.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>171901 - Contabilidade, inclusive serviços técnicos e auxiliares.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_20144.xlsx
+++ b/planos_empresas/plano_empresa_20144.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,6 +551,21 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>140101 - Lubrificação, limpeza, lustração, revisão, carga e recarga, conserto, restauração, blindagem, manutenção e conservação de máquinas, veículos, aparelhos, equipamentos, motores, elevadores ou de qualquer objeto (exceto peças e partes empregadas, que ficam sujeitas ao ICMS).</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planos_empresas/plano_empresa_20144.xlsx
+++ b/planos_empresas/plano_empresa_20144.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,6 +566,21 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>140201 - Assistência técnica.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
